--- a/dev/StructureDefinition-bc-organization.xlsx
+++ b/dev/StructureDefinition-bc-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T20:38:35+00:00</t>
+    <t>2026-01-23T00:06:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3017,7 +3017,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>158</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>163</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>168</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>173</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>183</v>
       </c>
@@ -3931,7 +3931,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>193</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>205</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>224</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>246</v>
       </c>
@@ -5073,7 +5073,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>260</v>
       </c>
@@ -5187,7 +5187,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>265</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>270</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>275</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>290</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>301</v>
       </c>
@@ -8631,12 +8631,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN59">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
